--- a/实验数据.xlsx
+++ b/实验数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\论文\FreTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC0A8FC-A4E0-4A87-8732-1AE0CC6CFC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3835C3B-478D-41F3-A4BC-679DD91F0FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70A24257-4B2D-47D6-9D9B-E74BB69E2E24}"/>
   </bookViews>
@@ -401,7 +401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -565,6 +565,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1065,13 +1071,13 @@
       <c r="D3" s="32">
         <v>0.35</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="55">
         <v>0.32600000000000001</v>
       </c>
       <c r="F3" s="41">
         <v>0.36299999999999999</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="40">
         <v>0.31900000000000001</v>
       </c>
       <c r="H3" s="5">
@@ -1648,10 +1654,10 @@
         <v>192</v>
       </c>
       <c r="C9" s="33">
-        <v>0.23799999999999999</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="D9" s="32">
-        <v>0.3</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="E9" s="4">
         <v>0.247</v>
@@ -1942,7 +1948,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="34">
-        <v>0.27700000000000002</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="D12" s="35">
         <v>0.32200000000000001</v>
@@ -2532,13 +2538,13 @@
       <c r="C18" s="26">
         <v>0.29699999999999999</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="56">
         <v>0.34399999999999997</v>
       </c>
       <c r="E18" s="40">
         <v>0.29299999999999998</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="54">
         <v>0.34599999999999997</v>
       </c>
       <c r="G18" s="6">
@@ -3020,10 +3026,10 @@
         <v>96</v>
       </c>
       <c r="C23" s="26">
-        <v>0.186</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="D23" s="27">
-        <v>0.26800000000000002</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="E23" s="36">
         <v>0.13800000000000001</v>
@@ -3118,10 +3124,10 @@
         <v>192</v>
       </c>
       <c r="C24" s="26">
-        <v>0.193</v>
+        <v>0.189</v>
       </c>
       <c r="D24" s="27">
-        <v>0.27500000000000002</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="E24" s="36">
         <v>0.158</v>
@@ -3216,10 +3222,10 @@
         <v>336</v>
       </c>
       <c r="C25" s="26">
-        <v>0.21</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="D25" s="27">
-        <v>0.29099999999999998</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="E25" s="36">
         <v>0.17399999999999999</v>
@@ -3314,10 +3320,10 @@
         <v>720</v>
       </c>
       <c r="C26" s="26">
-        <v>0.246</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="D26" s="27">
-        <v>0.32200000000000001</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="E26" s="33">
         <v>0.19900000000000001</v>
@@ -3412,10 +3418,10 @@
         <v>3</v>
       </c>
       <c r="C27" s="28">
-        <v>0.20799999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="D27" s="29">
-        <v>0.28899999999999998</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="E27" s="47">
         <v>0.16700000000000001</v>

--- a/实验数据.xlsx
+++ b/实验数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\论文\FreTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3835C3B-478D-41F3-A4BC-679DD91F0FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB6581B-9C7A-41A0-9971-236478F4886F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70A24257-4B2D-47D6-9D9B-E74BB69E2E24}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="32">
   <si>
     <t>Dataset</t>
   </si>
@@ -143,12 +143,20 @@
     <t>Autoformer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>ETTh2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,14 +167,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="4"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
@@ -401,7 +401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -414,7 +414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -423,10 +423,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -438,10 +435,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -474,10 +471,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -492,9 +489,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -510,31 +504,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -543,10 +537,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -561,16 +555,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -900,159 +897,159 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="24"/>
+      <c r="E1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="23"/>
-      <c r="G1" s="22" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="23"/>
-      <c r="I1" s="22" t="s">
+      <c r="H1" s="22"/>
+      <c r="I1" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="23"/>
-      <c r="K1" s="22" t="s">
+      <c r="J1" s="22"/>
+      <c r="K1" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="22" t="s">
+      <c r="L1" s="22"/>
+      <c r="M1" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="23"/>
-      <c r="O1" s="22" t="s">
+      <c r="N1" s="22"/>
+      <c r="O1" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="22" t="s">
+      <c r="P1" s="22"/>
+      <c r="Q1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="23"/>
-      <c r="S1" s="22" t="s">
+      <c r="R1" s="22"/>
+      <c r="S1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="23"/>
-      <c r="U1" s="22" t="s">
+      <c r="T1" s="22"/>
+      <c r="U1" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="23"/>
-      <c r="W1" s="22" t="s">
+      <c r="V1" s="22"/>
+      <c r="W1" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="22" t="s">
+      <c r="X1" s="22"/>
+      <c r="Y1" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="22" t="s">
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="22" t="s">
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="22" t="s">
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="23"/>
+      <c r="AF1" s="22"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="S2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="T2" s="20" t="s">
+      <c r="T2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="W2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="X2" s="20" t="s">
+      <c r="X2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="Y2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="Z2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="19" t="s">
+      <c r="AA2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="20" t="s">
+      <c r="AB2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AC2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AD2" s="20" t="s">
+      <c r="AD2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AF2" s="19" t="s">
         <v>14</v>
       </c>
       <c r="AG2" s="3"/>
@@ -1065,19 +1062,19 @@
       <c r="B3" s="3">
         <v>96</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="29">
         <v>0.313</v>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="30">
         <v>0.35</v>
       </c>
-      <c r="E3" s="55">
+      <c r="E3" s="52">
         <v>0.32600000000000001</v>
       </c>
-      <c r="F3" s="41">
+      <c r="F3" s="39">
         <v>0.36299999999999999</v>
       </c>
-      <c r="G3" s="40">
+      <c r="G3" s="38">
         <v>0.31900000000000001</v>
       </c>
       <c r="H3" s="5">
@@ -1163,10 +1160,10 @@
       <c r="B4" s="3">
         <v>192</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="31">
         <v>0.36499999999999999</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="30">
         <v>0.38</v>
       </c>
       <c r="E4" s="4">
@@ -1199,10 +1196,10 @@
       <c r="N4" s="7">
         <v>0.39200000000000002</v>
       </c>
-      <c r="O4" s="40">
+      <c r="O4" s="38">
         <v>0.36699999999999999</v>
       </c>
-      <c r="P4" s="41">
+      <c r="P4" s="39">
         <v>0.38500000000000001</v>
       </c>
       <c r="Q4" s="4">
@@ -1261,10 +1258,10 @@
       <c r="B5" s="3">
         <v>336</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="31">
         <v>0.39400000000000002</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="30">
         <v>0.40200000000000002</v>
       </c>
       <c r="E5" s="6">
@@ -1297,10 +1294,10 @@
       <c r="N5" s="7">
         <v>0.41499999999999998</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="38">
         <v>0.39900000000000002</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="39">
         <v>0.41</v>
       </c>
       <c r="Q5" s="4">
@@ -1359,10 +1356,10 @@
       <c r="B6" s="3">
         <v>720</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="37">
         <v>0.47</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="44">
         <v>0.44400000000000001</v>
       </c>
       <c r="E6" s="6">
@@ -1395,10 +1392,10 @@
       <c r="N6" s="7">
         <v>0.45</v>
       </c>
-      <c r="O6" s="36">
+      <c r="O6" s="34">
         <v>0.45400000000000001</v>
       </c>
-      <c r="P6" s="37">
+      <c r="P6" s="35">
         <v>0.439</v>
       </c>
       <c r="Q6" s="4">
@@ -1454,97 +1451,97 @@
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="32">
         <v>0.38500000000000001</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="33">
         <v>0.39400000000000002</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>0.39600000000000002</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>0.40500000000000003</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>0.39800000000000002</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <v>0.41099999999999998</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>0.39800000000000002</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <v>0.40500000000000003</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="11">
         <v>0.40699999999999997</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="12">
         <v>0.41</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="11">
         <v>0.41399999999999998</v>
       </c>
-      <c r="N7" s="13">
+      <c r="N7" s="12">
         <v>0.40699999999999997</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="40">
         <v>0.38700000000000001</v>
       </c>
-      <c r="P7" s="43">
+      <c r="P7" s="41">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="11">
         <v>0.51300000000000001</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="12">
         <v>0.496</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="11">
         <v>0.41899999999999998</v>
       </c>
-      <c r="T7" s="13">
+      <c r="T7" s="12">
         <v>0.41899999999999998</v>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="11">
         <v>0.4</v>
       </c>
-      <c r="V7" s="13">
+      <c r="V7" s="12">
         <v>0.40600000000000003</v>
       </c>
-      <c r="W7" s="12">
+      <c r="W7" s="11">
         <v>0.40300000000000002</v>
       </c>
-      <c r="X7" s="13">
+      <c r="X7" s="12">
         <v>0.40699999999999997</v>
       </c>
-      <c r="Y7" s="10">
+      <c r="Y7" s="9">
         <v>0.48499999999999999</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="Z7" s="10">
         <v>0.48099999999999998</v>
       </c>
-      <c r="AA7" s="10">
+      <c r="AA7" s="9">
         <v>0.44800000000000001</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AB7" s="10">
         <v>0.45200000000000001</v>
       </c>
-      <c r="AC7" s="10">
+      <c r="AC7" s="9">
         <v>0.48099999999999998</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AD7" s="10">
         <v>0.45600000000000002</v>
       </c>
-      <c r="AE7" s="10">
+      <c r="AE7" s="9">
         <v>0.58799999999999997</v>
       </c>
-      <c r="AF7" s="11">
+      <c r="AF7" s="10">
         <v>0.51700000000000002</v>
       </c>
     </row>
@@ -1555,22 +1552,22 @@
       <c r="B8" s="3">
         <v>96</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="37">
         <v>0.17399999999999999</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="30">
         <v>0.25600000000000001</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="42">
         <v>0.17299999999999999</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="36">
         <v>0.25600000000000001</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>0.17699999999999999</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>0.26200000000000001</v>
       </c>
       <c r="I8" s="6">
@@ -1594,7 +1591,7 @@
       <c r="O8" s="4">
         <v>0.17499999999999999</v>
       </c>
-      <c r="P8" s="41">
+      <c r="P8" s="39">
         <v>0.25900000000000001</v>
       </c>
       <c r="Q8" s="4">
@@ -1653,10 +1650,10 @@
       <c r="B9" s="3">
         <v>192</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="31">
         <v>0.23699999999999999</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="30">
         <v>0.29899999999999999</v>
       </c>
       <c r="E9" s="4">
@@ -1689,10 +1686,10 @@
       <c r="N9" s="7">
         <v>0.30399999999999999</v>
       </c>
-      <c r="O9" s="40">
+      <c r="O9" s="38">
         <v>0.24099999999999999</v>
       </c>
-      <c r="P9" s="41">
+      <c r="P9" s="39">
         <v>0.30199999999999999</v>
       </c>
       <c r="Q9" s="4">
@@ -1751,10 +1748,10 @@
       <c r="B10" s="3">
         <v>336</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="31">
         <v>0.30199999999999999</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="30">
         <v>0.34</v>
       </c>
       <c r="E10" s="6">
@@ -1787,10 +1784,10 @@
       <c r="N10" s="7">
         <v>0.34200000000000003</v>
       </c>
-      <c r="O10" s="40">
+      <c r="O10" s="38">
         <v>0.30499999999999999</v>
       </c>
-      <c r="P10" s="41">
+      <c r="P10" s="39">
         <v>0.34300000000000003</v>
       </c>
       <c r="Q10" s="4">
@@ -1849,10 +1846,10 @@
       <c r="B11" s="3">
         <v>720</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="31">
         <v>0.39400000000000002</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="30">
         <v>0.39500000000000002</v>
       </c>
       <c r="E11" s="6">
@@ -1882,13 +1879,13 @@
       <c r="M11" s="4">
         <v>0.40699999999999997</v>
       </c>
-      <c r="N11" s="41">
+      <c r="N11" s="39">
         <v>0.39800000000000002</v>
       </c>
-      <c r="O11" s="40">
+      <c r="O11" s="38">
         <v>0.40200000000000002</v>
       </c>
-      <c r="P11" s="54">
+      <c r="P11" s="51">
         <v>0.4</v>
       </c>
       <c r="Q11" s="4">
@@ -1944,97 +1941,97 @@
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="32">
         <v>0.27600000000000002</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="33">
         <v>0.32200000000000001</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>0.28299999999999997</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="10">
         <v>0.32800000000000001</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>0.28799999999999998</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="10">
         <v>0.33</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>0.28799999999999998</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <v>0.33200000000000002</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="11">
         <v>0.28799999999999998</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="12">
         <v>0.33200000000000002</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="11">
         <v>0.28599999999999998</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="12">
         <v>0.32700000000000001</v>
       </c>
-      <c r="O12" s="42">
+      <c r="O12" s="40">
         <v>0.28100000000000003</v>
       </c>
-      <c r="P12" s="43">
+      <c r="P12" s="41">
         <v>0.32600000000000001</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="11">
         <v>0.75700000000000001</v>
       </c>
-      <c r="R12" s="13">
+      <c r="R12" s="12">
         <v>0.61</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S12" s="11">
         <v>0.35799999999999998</v>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="12">
         <v>0.40400000000000003</v>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="11">
         <v>0.29099999999999998</v>
       </c>
-      <c r="V12" s="13">
+      <c r="V12" s="12">
         <v>0.33300000000000002</v>
       </c>
-      <c r="W12" s="12">
+      <c r="W12" s="11">
         <v>0.35</v>
       </c>
-      <c r="X12" s="13">
+      <c r="X12" s="12">
         <v>0.40100000000000002</v>
       </c>
-      <c r="Y12" s="10">
+      <c r="Y12" s="9">
         <v>0.57099999999999995</v>
       </c>
-      <c r="Z12" s="11">
+      <c r="Z12" s="10">
         <v>0.53700000000000003</v>
       </c>
-      <c r="AA12" s="10">
+      <c r="AA12" s="9">
         <v>0.30499999999999999</v>
       </c>
-      <c r="AB12" s="11">
+      <c r="AB12" s="10">
         <v>0.34899999999999998</v>
       </c>
-      <c r="AC12" s="10">
+      <c r="AC12" s="9">
         <v>0.30599999999999999</v>
       </c>
-      <c r="AD12" s="11">
+      <c r="AD12" s="10">
         <v>0.34699999999999998</v>
       </c>
-      <c r="AE12" s="10">
+      <c r="AE12" s="9">
         <v>0.32700000000000001</v>
       </c>
-      <c r="AF12" s="11">
+      <c r="AF12" s="10">
         <v>0.371</v>
       </c>
     </row>
@@ -2045,10 +2042,10 @@
       <c r="B13" s="3">
         <v>96</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="37">
         <v>0.38</v>
       </c>
-      <c r="D13" s="45">
+      <c r="D13" s="43">
         <v>0.39400000000000002</v>
       </c>
       <c r="E13" s="6">
@@ -2078,7 +2075,7 @@
       <c r="M13" s="4">
         <v>0.38600000000000001</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="39">
         <v>0.39500000000000002</v>
       </c>
       <c r="O13" s="4">
@@ -2117,7 +2114,7 @@
       <c r="Z13" s="5">
         <v>0.59899999999999998</v>
       </c>
-      <c r="AA13" s="36">
+      <c r="AA13" s="34">
         <v>0.376</v>
       </c>
       <c r="AB13" s="5">
@@ -2143,10 +2140,10 @@
       <c r="B14" s="3">
         <v>192</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="37">
         <v>0.434</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="43">
         <v>0.42299999999999999</v>
       </c>
       <c r="E14" s="6">
@@ -2176,7 +2173,7 @@
       <c r="M14" s="4">
         <v>0.437</v>
       </c>
-      <c r="N14" s="41">
+      <c r="N14" s="39">
         <v>0.42399999999999999</v>
       </c>
       <c r="O14" s="4">
@@ -2215,7 +2212,7 @@
       <c r="Z14" s="5">
         <v>0.63100000000000001</v>
       </c>
-      <c r="AA14" s="36">
+      <c r="AA14" s="34">
         <v>0.42</v>
       </c>
       <c r="AB14" s="5">
@@ -2241,10 +2238,10 @@
       <c r="B15" s="3">
         <v>336</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="37">
         <v>0.47099999999999997</v>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="43">
         <v>0.441</v>
       </c>
       <c r="E15" s="6">
@@ -2274,7 +2271,7 @@
       <c r="M15" s="4">
         <v>0.47899999999999998</v>
       </c>
-      <c r="N15" s="41">
+      <c r="N15" s="39">
         <v>0.44600000000000001</v>
       </c>
       <c r="O15" s="6">
@@ -2313,7 +2310,7 @@
       <c r="Z15" s="5">
         <v>0.65900000000000003</v>
       </c>
-      <c r="AA15" s="36">
+      <c r="AA15" s="34">
         <v>0.45900000000000002</v>
       </c>
       <c r="AB15" s="5">
@@ -2339,10 +2336,10 @@
       <c r="B16" s="3">
         <v>720</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="37">
         <v>0.49399999999999999</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="43">
         <v>0.47</v>
       </c>
       <c r="E16" s="6">
@@ -2369,10 +2366,10 @@
       <c r="L16" s="5">
         <v>0.49099999999999999</v>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="34">
         <v>0.48099999999999998</v>
       </c>
-      <c r="N16" s="37">
+      <c r="N16" s="35">
         <v>0.47</v>
       </c>
       <c r="O16" s="6">
@@ -2434,97 +2431,97 @@
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="51">
+      <c r="C17" s="49">
         <v>0.44400000000000001</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="33">
         <v>0.432</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>0.45600000000000002</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <v>0.44700000000000001</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>0.45200000000000001</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <v>0.45200000000000001</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>0.45500000000000002</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <v>0.45</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>0.45400000000000001</v>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="10">
         <v>0.44700000000000001</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>0.44600000000000001</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="41">
         <v>0.434</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="9">
         <v>0.46899999999999997</v>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="10">
         <v>0.45400000000000001</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="9">
         <v>0.52900000000000003</v>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="10">
         <v>0.52200000000000002</v>
       </c>
-      <c r="S17" s="10">
+      <c r="S17" s="9">
         <v>0.54100000000000004</v>
       </c>
-      <c r="T17" s="11">
+      <c r="T17" s="10">
         <v>0.50700000000000001</v>
       </c>
-      <c r="U17" s="10">
+      <c r="U17" s="9">
         <v>0.45800000000000002</v>
       </c>
-      <c r="V17" s="11">
+      <c r="V17" s="10">
         <v>0.45</v>
       </c>
-      <c r="W17" s="10">
+      <c r="W17" s="9">
         <v>0.45600000000000002</v>
       </c>
-      <c r="X17" s="11">
+      <c r="X17" s="10">
         <v>0.45200000000000001</v>
       </c>
-      <c r="Y17" s="10">
+      <c r="Y17" s="9">
         <v>0.747</v>
       </c>
-      <c r="Z17" s="11">
+      <c r="Z17" s="10">
         <v>0.64700000000000002</v>
       </c>
-      <c r="AA17" s="47">
+      <c r="AA17" s="45">
         <v>0.44</v>
       </c>
-      <c r="AB17" s="11">
+      <c r="AB17" s="10">
         <v>0.46</v>
       </c>
-      <c r="AC17" s="10">
+      <c r="AC17" s="9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="AD17" s="11">
+      <c r="AD17" s="10">
         <v>0.53700000000000003</v>
       </c>
-      <c r="AE17" s="10">
+      <c r="AE17" s="9">
         <v>0.496</v>
       </c>
-      <c r="AF17" s="11">
+      <c r="AF17" s="10">
         <v>0.48699999999999999</v>
       </c>
     </row>
@@ -2535,16 +2532,16 @@
       <c r="B18" s="3">
         <v>96</v>
       </c>
-      <c r="C18" s="26">
-        <v>0.29699999999999999</v>
-      </c>
-      <c r="D18" s="56">
-        <v>0.34399999999999997</v>
-      </c>
-      <c r="E18" s="40">
+      <c r="C18" s="37">
         <v>0.29299999999999998</v>
       </c>
-      <c r="F18" s="54">
+      <c r="D18" s="53">
+        <v>0.34</v>
+      </c>
+      <c r="E18" s="38">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="F18" s="51">
         <v>0.34599999999999997</v>
       </c>
       <c r="G18" s="6">
@@ -2565,10 +2562,10 @@
       <c r="L18" s="5">
         <v>0.34899999999999998</v>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="34">
         <v>0.28799999999999998</v>
       </c>
-      <c r="N18" s="37">
+      <c r="N18" s="35">
         <v>0.33800000000000002</v>
       </c>
       <c r="O18" s="6">
@@ -2633,16 +2630,16 @@
       <c r="B19" s="3">
         <v>192</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="31">
+        <v>0.374</v>
+      </c>
+      <c r="D19" s="43">
         <v>0.39</v>
-      </c>
-      <c r="D19" s="27">
-        <v>0.40500000000000003</v>
       </c>
       <c r="E19" s="4">
         <v>0.378</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="48">
         <v>0.39900000000000002</v>
       </c>
       <c r="G19" s="6">
@@ -2651,10 +2648,10 @@
       <c r="H19" s="5">
         <v>0.41399999999999998</v>
       </c>
-      <c r="I19" s="40">
+      <c r="I19" s="38">
         <v>0.376</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="51">
         <v>0.39600000000000002</v>
       </c>
       <c r="K19" s="6">
@@ -2663,10 +2660,10 @@
       <c r="L19" s="5">
         <v>0.4</v>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="34">
         <v>0.374</v>
       </c>
-      <c r="N19" s="37">
+      <c r="N19" s="35">
         <v>0.39</v>
       </c>
       <c r="O19" s="6">
@@ -2726,18 +2723,18 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B20" s="3">
         <v>336</v>
       </c>
-      <c r="C20" s="26">
-        <v>0.42699999999999999</v>
-      </c>
-      <c r="D20" s="27">
-        <v>0.441</v>
-      </c>
-      <c r="E20" s="40">
+      <c r="C20" s="31">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="D20" s="43">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="E20" s="52">
         <v>0.42099999999999999</v>
       </c>
       <c r="F20" s="5">
@@ -2752,19 +2749,19 @@
       <c r="I20" s="6">
         <v>0.42399999999999999</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="54">
         <v>0.43099999999999999</v>
       </c>
       <c r="K20" s="6">
         <v>0.42799999999999999</v>
       </c>
-      <c r="L20" s="50">
+      <c r="L20" s="54">
         <v>0.432</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="38">
         <v>0.41499999999999998</v>
       </c>
-      <c r="N20" s="37">
+      <c r="N20" s="39">
         <v>0.42599999999999999</v>
       </c>
       <c r="O20" s="6">
@@ -2829,19 +2826,19 @@
       <c r="B21" s="3">
         <v>720</v>
       </c>
-      <c r="C21" s="26">
-        <v>0.432</v>
-      </c>
-      <c r="D21" s="27">
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="E21" s="36">
+      <c r="C21" s="25">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="D21" s="26">
+        <v>0.441</v>
+      </c>
+      <c r="E21" s="34">
         <v>0.40699999999999997</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="35">
         <v>0.435</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="38">
         <v>0.41699999999999998</v>
       </c>
       <c r="H21" s="5">
@@ -2862,7 +2859,7 @@
       <c r="M21" s="6">
         <v>0.42</v>
       </c>
-      <c r="N21" s="41">
+      <c r="N21" s="39">
         <v>0.44</v>
       </c>
       <c r="O21" s="6">
@@ -2924,117 +2921,117 @@
       <c r="A22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="28">
-        <v>0.38600000000000001</v>
-      </c>
-      <c r="D22" s="30">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="E22" s="42">
+      <c r="C22" s="49">
         <v>0.375</v>
       </c>
-      <c r="F22" s="43">
+      <c r="D22" s="50">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="E22" s="40">
+        <v>0.375</v>
+      </c>
+      <c r="F22" s="55">
         <v>0.40300000000000002</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>0.39600000000000002</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="10">
         <v>0.41699999999999998</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="9">
         <v>0.38100000000000001</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="10">
         <v>0.40500000000000003</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="9">
         <v>0.38300000000000001</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="10">
         <v>0.40699999999999997</v>
       </c>
-      <c r="M22" s="47">
+      <c r="M22" s="45">
         <v>0.374</v>
       </c>
-      <c r="N22" s="48">
+      <c r="N22" s="46">
         <v>0.39800000000000002</v>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="9">
         <v>0.38700000000000001</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="10">
         <v>0.40699999999999997</v>
       </c>
-      <c r="Q22" s="10">
+      <c r="Q22" s="9">
         <v>0.94199999999999995</v>
       </c>
-      <c r="R22" s="11">
+      <c r="R22" s="10">
         <v>0.68400000000000005</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S22" s="9">
         <v>0.61099999999999999</v>
       </c>
-      <c r="T22" s="11">
+      <c r="T22" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="U22" s="10">
+      <c r="U22" s="9">
         <v>0.41399999999999998</v>
       </c>
-      <c r="V22" s="11">
+      <c r="V22" s="10">
         <v>0.42699999999999999</v>
       </c>
-      <c r="W22" s="10">
+      <c r="W22" s="9">
         <v>0.55900000000000005</v>
       </c>
-      <c r="X22" s="11">
+      <c r="X22" s="10">
         <v>0.51500000000000001</v>
       </c>
-      <c r="Y22" s="10">
+      <c r="Y22" s="9">
         <v>0.95399999999999996</v>
       </c>
-      <c r="Z22" s="11">
+      <c r="Z22" s="10">
         <v>0.72299999999999998</v>
       </c>
-      <c r="AA22" s="10">
+      <c r="AA22" s="9">
         <v>0.437</v>
       </c>
-      <c r="AB22" s="11">
+      <c r="AB22" s="10">
         <v>0.44900000000000001</v>
       </c>
-      <c r="AC22" s="10">
+      <c r="AC22" s="9">
         <v>0.52600000000000002</v>
       </c>
-      <c r="AD22" s="11">
+      <c r="AD22" s="10">
         <v>0.51600000000000001</v>
       </c>
-      <c r="AE22" s="10">
+      <c r="AE22" s="9">
         <v>0.45</v>
       </c>
-      <c r="AF22" s="11">
+      <c r="AF22" s="10">
         <v>0.45900000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3">
         <v>96</v>
       </c>
-      <c r="C23" s="26">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="D23" s="27">
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="E23" s="36">
+      <c r="C23" s="25">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="D23" s="26">
+        <v>0.255</v>
+      </c>
+      <c r="E23" s="34">
         <v>0.13800000000000001</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="39">
         <v>0.23599999999999999</v>
       </c>
       <c r="G23" s="6">
@@ -3043,10 +3040,10 @@
       <c r="H23" s="5">
         <v>0.27400000000000002</v>
       </c>
-      <c r="I23" s="40">
+      <c r="I23" s="38">
         <v>0.13900000000000001</v>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="35">
         <v>0.23499999999999999</v>
       </c>
       <c r="K23" s="4">
@@ -3123,16 +3120,16 @@
       <c r="B24" s="3">
         <v>192</v>
       </c>
-      <c r="C24" s="26">
-        <v>0.189</v>
-      </c>
-      <c r="D24" s="27">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="E24" s="36">
+      <c r="C24" s="25">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D24" s="26">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="E24" s="34">
         <v>0.158</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="39">
         <v>0.255</v>
       </c>
       <c r="G24" s="6">
@@ -3141,16 +3138,16 @@
       <c r="H24" s="5">
         <v>0.29199999999999998</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="37">
         <v>0.159</v>
       </c>
-      <c r="J24" s="41">
+      <c r="J24" s="39">
         <v>0.255</v>
       </c>
       <c r="K24" s="6">
         <v>0.16200000000000001</v>
       </c>
-      <c r="L24" s="37">
+      <c r="L24" s="35">
         <v>0.253</v>
       </c>
       <c r="M24" s="6">
@@ -3221,16 +3218,16 @@
       <c r="B25" s="3">
         <v>336</v>
       </c>
-      <c r="C25" s="26">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="D25" s="27">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="E25" s="36">
+      <c r="C25" s="25">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="D25" s="26">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="E25" s="34">
         <v>0.17399999999999999</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="39">
         <v>0.27100000000000002</v>
       </c>
       <c r="G25" s="6">
@@ -3239,7 +3236,7 @@
       <c r="H25" s="5">
         <v>0.30199999999999999</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="37">
         <v>0.17599999999999999</v>
       </c>
       <c r="J25" s="5">
@@ -3248,7 +3245,7 @@
       <c r="K25" s="6">
         <v>0.17799999999999999</v>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="35">
         <v>0.26900000000000002</v>
       </c>
       <c r="M25" s="6">
@@ -3319,16 +3316,16 @@
       <c r="B26" s="3">
         <v>720</v>
       </c>
-      <c r="C26" s="26">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="D26" s="27">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="E26" s="33">
+      <c r="C26" s="25">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="D26" s="26">
+        <v>0.314</v>
+      </c>
+      <c r="E26" s="31">
         <v>0.19900000000000001</v>
       </c>
-      <c r="F26" s="49">
+      <c r="F26" s="47">
         <v>0.29499999999999998</v>
       </c>
       <c r="G26" s="6">
@@ -3337,10 +3334,10 @@
       <c r="H26" s="5">
         <v>0.33200000000000002</v>
       </c>
-      <c r="I26" s="39">
+      <c r="I26" s="37">
         <v>0.20399999999999999</v>
       </c>
-      <c r="J26" s="50">
+      <c r="J26" s="48">
         <v>0.29799999999999999</v>
       </c>
       <c r="K26" s="6">
@@ -3414,97 +3411,97 @@
       <c r="A27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="28">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="D27" s="29">
-        <v>0.28599999999999998</v>
-      </c>
-      <c r="E27" s="47">
+      <c r="C27" s="27">
+        <v>0.192</v>
+      </c>
+      <c r="D27" s="28">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="E27" s="45">
         <v>0.16700000000000001</v>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="46">
         <v>0.26400000000000001</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>0.19400000000000001</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="10">
         <v>0.3</v>
       </c>
-      <c r="I27" s="51">
+      <c r="I27" s="49">
         <v>0.17</v>
       </c>
-      <c r="J27" s="52">
+      <c r="J27" s="50">
         <v>0.26500000000000001</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="9">
         <v>0.17799999999999999</v>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="10">
         <v>0.27</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="9">
         <v>0.219</v>
       </c>
-      <c r="N27" s="11">
+      <c r="N27" s="10">
         <v>0.29799999999999999</v>
       </c>
-      <c r="O27" s="10">
+      <c r="O27" s="9">
         <v>0.20499999999999999</v>
       </c>
-      <c r="P27" s="11">
+      <c r="P27" s="10">
         <v>0.28999999999999998</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="9">
         <v>0.24399999999999999</v>
       </c>
-      <c r="R27" s="11">
+      <c r="R27" s="10">
         <v>0.33400000000000002</v>
       </c>
-      <c r="S27" s="10">
+      <c r="S27" s="9">
         <v>0.251</v>
       </c>
-      <c r="T27" s="11">
+      <c r="T27" s="10">
         <v>0.34399999999999997</v>
       </c>
-      <c r="U27" s="10">
+      <c r="U27" s="9">
         <v>0.192</v>
       </c>
-      <c r="V27" s="11">
+      <c r="V27" s="10">
         <v>0.29499999999999998</v>
       </c>
-      <c r="W27" s="10">
+      <c r="W27" s="9">
         <v>0.21199999999999999</v>
       </c>
-      <c r="X27" s="11">
+      <c r="X27" s="10">
         <v>0.3</v>
       </c>
-      <c r="Y27" s="10">
+      <c r="Y27" s="9">
         <v>0.26800000000000002</v>
       </c>
-      <c r="Z27" s="11">
+      <c r="Z27" s="10">
         <v>0.36499999999999999</v>
       </c>
-      <c r="AA27" s="10">
+      <c r="AA27" s="9">
         <v>0.214</v>
       </c>
-      <c r="AB27" s="11">
+      <c r="AB27" s="10">
         <v>0.32700000000000001</v>
       </c>
-      <c r="AC27" s="10">
+      <c r="AC27" s="9">
         <v>0.193</v>
       </c>
-      <c r="AD27" s="11">
+      <c r="AD27" s="10">
         <v>0.29599999999999999</v>
       </c>
-      <c r="AE27" s="10">
+      <c r="AE27" s="9">
         <v>0.22700000000000001</v>
       </c>
-      <c r="AF27" s="11">
+      <c r="AF27" s="10">
         <v>0.33800000000000002</v>
       </c>
     </row>
@@ -3515,13 +3512,13 @@
       <c r="B28" s="3">
         <v>96</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="31">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="D28" s="45">
+      <c r="D28" s="43">
         <v>0.20100000000000001</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="38">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="F28" s="5">
@@ -3533,13 +3530,13 @@
       <c r="H28" s="5">
         <v>0.23</v>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="38">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="J28" s="7">
         <v>0.20699999999999999</v>
       </c>
-      <c r="K28" s="40">
+      <c r="K28" s="38">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="L28" s="5">
@@ -3554,7 +3551,7 @@
       <c r="O28" s="6">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="P28" s="41">
+      <c r="P28" s="39">
         <v>0.20499999999999999</v>
       </c>
       <c r="Q28" s="6">
@@ -3613,10 +3610,10 @@
       <c r="B29" s="3">
         <v>192</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="31">
         <v>0.17199999999999999</v>
       </c>
-      <c r="D29" s="45">
+      <c r="D29" s="43">
         <v>0.29499999999999998</v>
       </c>
       <c r="E29" s="6">
@@ -3640,7 +3637,7 @@
       <c r="K29" s="6">
         <v>0.17699999999999999</v>
       </c>
-      <c r="L29" s="41">
+      <c r="L29" s="39">
         <v>0.29899999999999999</v>
       </c>
       <c r="M29" s="6">
@@ -3649,10 +3646,10 @@
       <c r="N29" s="5">
         <v>0.307</v>
       </c>
-      <c r="O29" s="40">
+      <c r="O29" s="38">
         <v>0.17599999999999999</v>
       </c>
-      <c r="P29" s="41">
+      <c r="P29" s="39">
         <v>0.29899999999999999</v>
       </c>
       <c r="Q29" s="6">
@@ -3673,7 +3670,7 @@
       <c r="V29" s="5">
         <v>0.34399999999999997</v>
       </c>
-      <c r="W29" s="8">
+      <c r="W29" s="38">
         <v>0.17599999999999999</v>
       </c>
       <c r="X29" s="5">
@@ -3711,16 +3708,16 @@
       <c r="B30" s="3">
         <v>336</v>
       </c>
-      <c r="C30" s="26">
-        <v>0.33</v>
-      </c>
-      <c r="D30" s="27">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="E30" s="39">
+      <c r="C30" s="25">
+        <v>0.32</v>
+      </c>
+      <c r="D30" s="26">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="E30" s="37">
         <v>0.32500000000000001</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="48">
         <v>0.41299999999999998</v>
       </c>
       <c r="G30" s="6">
@@ -3747,10 +3744,10 @@
       <c r="N30" s="5">
         <v>0.432</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="34">
         <v>0.30099999999999999</v>
       </c>
-      <c r="P30" s="37">
+      <c r="P30" s="35">
         <v>0.39700000000000002</v>
       </c>
       <c r="Q30" s="6">
@@ -3809,16 +3806,16 @@
       <c r="B31" s="3">
         <v>720</v>
       </c>
-      <c r="C31" s="26">
-        <v>0.88200000000000001</v>
-      </c>
-      <c r="D31" s="27">
-        <v>0.70099999999999996</v>
-      </c>
-      <c r="E31" s="39">
+      <c r="C31" s="37">
+        <v>0.84899999999999998</v>
+      </c>
+      <c r="D31" s="53">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="E31" s="25">
         <v>0.85799999999999998</v>
       </c>
-      <c r="F31" s="50">
+      <c r="F31" s="54">
         <v>0.69799999999999995</v>
       </c>
       <c r="G31" s="6">
@@ -3833,10 +3830,10 @@
       <c r="J31" s="5">
         <v>0.70299999999999996</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="34">
         <v>0.84699999999999998</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="35">
         <v>0.69099999999999995</v>
       </c>
       <c r="M31" s="6">
@@ -3904,97 +3901,97 @@
       <c r="A32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="28">
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="D32" s="35">
+      <c r="C32" s="32">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="D32" s="33">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="F32" s="10">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="K32" s="49">
+        <v>0.36</v>
+      </c>
+      <c r="L32" s="50">
         <v>0.40300000000000002</v>
       </c>
-      <c r="E32" s="10">
-        <v>0.36199999999999999</v>
-      </c>
-      <c r="F32" s="11">
-        <v>0.40500000000000003</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="H32" s="11">
-        <v>0.43</v>
-      </c>
-      <c r="I32" s="10">
+      <c r="M32" s="9">
+        <v>0.378</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="O32" s="9">
         <v>0.36699999999999999</v>
       </c>
-      <c r="J32" s="11">
-        <v>0.40799999999999997</v>
-      </c>
-      <c r="K32" s="34">
-        <v>0.36</v>
-      </c>
-      <c r="L32" s="53">
-        <v>0.40300000000000002</v>
-      </c>
-      <c r="M32" s="10">
-        <v>0.378</v>
-      </c>
-      <c r="N32" s="11">
-        <v>0.41699999999999998</v>
-      </c>
-      <c r="O32" s="10">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="P32" s="11">
+      <c r="P32" s="10">
         <v>0.40400000000000003</v>
       </c>
-      <c r="Q32" s="10">
+      <c r="Q32" s="9">
         <v>0.94</v>
       </c>
-      <c r="R32" s="11">
+      <c r="R32" s="10">
         <v>0.70699999999999996</v>
       </c>
-      <c r="S32" s="10">
+      <c r="S32" s="9">
         <v>0.37</v>
       </c>
-      <c r="T32" s="11">
+      <c r="T32" s="10">
         <v>0.41299999999999998</v>
       </c>
-      <c r="U32" s="10">
+      <c r="U32" s="9">
         <v>0.41599999999999998</v>
       </c>
-      <c r="V32" s="11">
+      <c r="V32" s="10">
         <v>0.443</v>
       </c>
-      <c r="W32" s="10">
+      <c r="W32" s="9">
         <v>0.35399999999999998</v>
       </c>
-      <c r="X32" s="11">
+      <c r="X32" s="10">
         <v>0.41399999999999998</v>
       </c>
-      <c r="Y32" s="10">
+      <c r="Y32" s="9">
         <v>0.75</v>
       </c>
-      <c r="Z32" s="11">
+      <c r="Z32" s="10">
         <v>0.626</v>
       </c>
-      <c r="AA32" s="10">
+      <c r="AA32" s="9">
         <v>0.51900000000000002</v>
       </c>
-      <c r="AB32" s="11">
+      <c r="AB32" s="10">
         <v>0.42899999999999999</v>
       </c>
-      <c r="AC32" s="10">
+      <c r="AC32" s="9">
         <v>0.46100000000000002</v>
       </c>
-      <c r="AD32" s="11">
+      <c r="AD32" s="10">
         <v>0.45400000000000001</v>
       </c>
-      <c r="AE32" s="10">
+      <c r="AE32" s="9">
         <v>0.61299999999999999</v>
       </c>
-      <c r="AF32" s="11">
+      <c r="AF32" s="10">
         <v>0.53900000000000003</v>
       </c>
     </row>
@@ -4005,16 +4002,16 @@
       <c r="B33" s="3">
         <v>96</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="31">
         <v>0.153</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="30">
         <v>0.2</v>
       </c>
       <c r="E33" s="4">
         <v>0.161</v>
       </c>
-      <c r="F33" s="41">
+      <c r="F33" s="39">
         <v>0.20399999999999999</v>
       </c>
       <c r="G33" s="6">
@@ -4047,7 +4044,7 @@
       <c r="P33" s="5">
         <v>0.218</v>
       </c>
-      <c r="Q33" s="40">
+      <c r="Q33" s="38">
         <v>0.158</v>
       </c>
       <c r="R33" s="5">
@@ -4103,16 +4100,16 @@
       <c r="B34" s="3">
         <v>192</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="31">
         <v>0.20200000000000001</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="30">
         <v>0.247</v>
       </c>
       <c r="E34" s="6">
         <v>0.21299999999999999</v>
       </c>
-      <c r="F34" s="41">
+      <c r="F34" s="39">
         <v>0.252</v>
       </c>
       <c r="G34" s="4">
@@ -4145,7 +4142,7 @@
       <c r="P34" s="5">
         <v>0.25900000000000001</v>
       </c>
-      <c r="Q34" s="40">
+      <c r="Q34" s="38">
         <v>0.20599999999999999</v>
       </c>
       <c r="R34" s="5">
@@ -4201,19 +4198,19 @@
       <c r="B35" s="3">
         <v>336</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="31">
         <v>0.26200000000000001</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="30">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E35" s="40">
+      <c r="E35" s="38">
         <v>0.27200000000000002</v>
       </c>
-      <c r="F35" s="41">
+      <c r="F35" s="39">
         <v>0.29499999999999998</v>
       </c>
-      <c r="G35" s="40">
+      <c r="G35" s="38">
         <v>0.27200000000000002</v>
       </c>
       <c r="H35" s="5">
@@ -4243,7 +4240,7 @@
       <c r="P35" s="5">
         <v>0.29699999999999999</v>
       </c>
-      <c r="Q35" s="40">
+      <c r="Q35" s="38">
         <v>0.27200000000000002</v>
       </c>
       <c r="R35" s="5">
@@ -4299,19 +4296,19 @@
       <c r="B36" s="3">
         <v>720</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="31">
         <v>0.34300000000000003</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="30">
         <v>0.34399999999999997</v>
       </c>
       <c r="E36" s="6">
         <v>0.35199999999999998</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="39">
         <v>0.34699999999999998</v>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="38">
         <v>0.35</v>
       </c>
       <c r="H36" s="5">
@@ -4326,7 +4323,7 @@
       <c r="K36" s="6">
         <v>0.35799999999999998</v>
       </c>
-      <c r="L36" s="41">
+      <c r="L36" s="39">
         <v>0.34699999999999998</v>
       </c>
       <c r="M36" s="6">
@@ -4359,7 +4356,7 @@
       <c r="V36" s="5">
         <v>0.35899999999999999</v>
       </c>
-      <c r="W36" s="40">
+      <c r="W36" s="38">
         <v>0.34499999999999997</v>
       </c>
       <c r="X36" s="5">
@@ -4394,97 +4391,97 @@
       <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="32">
         <v>0.24</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="30">
         <v>0.27</v>
       </c>
-      <c r="E37" s="42">
+      <c r="E37" s="40">
         <v>0.249</v>
       </c>
-      <c r="F37" s="43">
+      <c r="F37" s="41">
         <v>0.27400000000000002</v>
       </c>
-      <c r="G37" s="42">
+      <c r="G37" s="40">
         <v>0.249</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="10">
         <v>0.27800000000000002</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="11">
         <v>0.251</v>
       </c>
-      <c r="J37" s="11">
+      <c r="J37" s="10">
         <v>0.27600000000000002</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="9">
         <v>0.25800000000000001</v>
       </c>
-      <c r="L37" s="11">
+      <c r="L37" s="10">
         <v>0.27800000000000002</v>
       </c>
-      <c r="M37" s="10">
+      <c r="M37" s="9">
         <v>0.27200000000000002</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="10">
         <v>0.29099999999999998</v>
       </c>
-      <c r="O37" s="10">
+      <c r="O37" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="P37" s="11">
+      <c r="P37" s="10">
         <v>0.28100000000000003</v>
       </c>
-      <c r="Q37" s="10">
+      <c r="Q37" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="R37" s="11">
+      <c r="R37" s="10">
         <v>0.315</v>
       </c>
-      <c r="S37" s="10">
+      <c r="S37" s="9">
         <v>0.27100000000000002</v>
       </c>
-      <c r="T37" s="11">
+      <c r="T37" s="10">
         <v>0.32</v>
       </c>
-      <c r="U37" s="10">
+      <c r="U37" s="9">
         <v>0.25900000000000001</v>
       </c>
-      <c r="V37" s="11">
+      <c r="V37" s="10">
         <v>0.28699999999999998</v>
       </c>
-      <c r="W37" s="10">
+      <c r="W37" s="9">
         <v>0.26500000000000001</v>
       </c>
-      <c r="X37" s="11">
+      <c r="X37" s="10">
         <v>0.317</v>
       </c>
-      <c r="Y37" s="10">
+      <c r="Y37" s="9">
         <v>0.29199999999999998</v>
       </c>
-      <c r="Z37" s="11">
+      <c r="Z37" s="10">
         <v>0.36299999999999999</v>
       </c>
-      <c r="AA37" s="10">
+      <c r="AA37" s="9">
         <v>0.309</v>
       </c>
-      <c r="AB37" s="11">
+      <c r="AB37" s="10">
         <v>0.36</v>
       </c>
-      <c r="AC37" s="10">
+      <c r="AC37" s="9">
         <v>0.28799999999999998</v>
       </c>
-      <c r="AD37" s="11">
+      <c r="AD37" s="10">
         <v>0.314</v>
       </c>
-      <c r="AE37" s="10">
+      <c r="AE37" s="9">
         <v>0.33800000000000002</v>
       </c>
-      <c r="AF37" s="11">
+      <c r="AF37" s="10">
         <v>0.38200000000000001</v>
       </c>
     </row>
@@ -4492,97 +4489,97 @@
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C38" s="17">
-        <v>15</v>
-      </c>
-      <c r="D38" s="16">
-        <v>22</v>
-      </c>
-      <c r="E38" s="17">
+      <c r="C38" s="16">
+        <v>17</v>
+      </c>
+      <c r="D38" s="15">
+        <v>24</v>
+      </c>
+      <c r="E38" s="16">
         <v>7</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="15">
         <v>4</v>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="16">
         <v>0</v>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="15">
         <v>0</v>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="16">
         <v>0</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="15">
         <v>1</v>
       </c>
-      <c r="K38" s="18">
+      <c r="K38" s="17">
         <v>2</v>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="15">
         <v>4</v>
       </c>
-      <c r="M38" s="18">
+      <c r="M38" s="17">
         <v>5</v>
       </c>
-      <c r="N38" s="16">
+      <c r="N38" s="15">
         <v>5</v>
       </c>
-      <c r="O38" s="18">
+      <c r="O38" s="17">
         <v>2</v>
       </c>
-      <c r="P38" s="16">
+      <c r="P38" s="15">
         <v>2</v>
       </c>
-      <c r="Q38" s="18">
+      <c r="Q38" s="17">
         <v>3</v>
       </c>
-      <c r="R38" s="16">
+      <c r="R38" s="15">
         <v>0</v>
       </c>
-      <c r="S38" s="17">
+      <c r="S38" s="16">
         <v>0</v>
       </c>
-      <c r="T38" s="16">
+      <c r="T38" s="15">
         <v>0</v>
       </c>
-      <c r="U38" s="17">
+      <c r="U38" s="16">
         <v>0</v>
       </c>
-      <c r="V38" s="16">
+      <c r="V38" s="15">
         <v>0</v>
       </c>
-      <c r="W38" s="17">
+      <c r="W38" s="16">
         <v>0</v>
       </c>
-      <c r="X38" s="16">
+      <c r="X38" s="15">
         <v>0</v>
       </c>
-      <c r="Y38" s="17">
+      <c r="Y38" s="16">
         <v>0</v>
       </c>
-      <c r="Z38" s="16">
+      <c r="Z38" s="15">
         <v>0</v>
       </c>
-      <c r="AA38" s="17">
+      <c r="AA38" s="16">
         <v>4</v>
       </c>
-      <c r="AB38" s="16">
+      <c r="AB38" s="15">
         <v>0</v>
       </c>
-      <c r="AC38" s="17">
+      <c r="AC38" s="16">
         <v>0</v>
       </c>
-      <c r="AD38" s="16">
+      <c r="AD38" s="15">
         <v>0</v>
       </c>
-      <c r="AE38" s="17">
+      <c r="AE38" s="16">
         <v>0</v>
       </c>
-      <c r="AF38" s="16">
+      <c r="AF38" s="15">
         <v>0</v>
       </c>
     </row>

--- a/实验数据.xlsx
+++ b/实验数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\论文\FreTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB6581B-9C7A-41A0-9971-236478F4886F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CB917F-5A57-4B41-8D1E-82C8C710112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{70A24257-4B2D-47D6-9D9B-E74BB69E2E24}"/>
   </bookViews>
@@ -3023,10 +3023,10 @@
         <v>96</v>
       </c>
       <c r="C23" s="25">
-        <v>0.16600000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="D23" s="26">
-        <v>0.255</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="E23" s="34">
         <v>0.13800000000000001</v>
@@ -3121,10 +3121,10 @@
         <v>192</v>
       </c>
       <c r="C24" s="25">
-        <v>0.17499999999999999</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="D24" s="26">
-        <v>0.26200000000000001</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="E24" s="34">
         <v>0.158</v>
@@ -3219,10 +3219,10 @@
         <v>336</v>
       </c>
       <c r="C25" s="25">
-        <v>0.19500000000000001</v>
+        <v>0.186</v>
       </c>
       <c r="D25" s="26">
-        <v>0.28199999999999997</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="E25" s="34">
         <v>0.17399999999999999</v>
@@ -3317,10 +3317,10 @@
         <v>720</v>
       </c>
       <c r="C26" s="25">
-        <v>0.23400000000000001</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="D26" s="26">
-        <v>0.314</v>
+        <v>0.31</v>
       </c>
       <c r="E26" s="31">
         <v>0.19900000000000001</v>
@@ -3415,10 +3415,10 @@
         <v>3</v>
       </c>
       <c r="C27" s="27">
-        <v>0.192</v>
+        <v>0.184</v>
       </c>
       <c r="D27" s="28">
-        <v>0.27800000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="E27" s="45">
         <v>0.16700000000000001</v>
@@ -3708,16 +3708,16 @@
       <c r="B30" s="3">
         <v>336</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="37">
         <v>0.32</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="53">
         <v>0.40799999999999997</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="25">
         <v>0.32500000000000001</v>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="54">
         <v>0.41299999999999998</v>
       </c>
       <c r="G30" s="6">
@@ -4493,7 +4493,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" s="15">
         <v>24</v>
